--- a/GameData/DataTables/Business/BossPhaseConfig.xlsx
+++ b/GameData/DataTables/Business/BossPhaseConfig.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
   <si>
     <t>#</t>
   </si>
   <si>
-    <t>Business table migrated from LegacyProjectArchive/Assets/Resources/DataTable/BossPhaseConfig.json. GF_X Id is numeric; original business keys are preserved as data columns.</t>
+    <t>Deterministic three-phase Boss configuration with 60% and 30% transitions.</t>
   </si>
   <si>
     <t>Id</t>
@@ -35,6 +37,9 @@
     <t>HPThreshold</t>
   </si>
   <si>
+    <t>AbilityIds</t>
+  </si>
+  <si>
     <t>NewSkillIds</t>
   </si>
   <si>
@@ -59,49 +64,52 @@
     <t>float</t>
   </si>
   <si>
-    <t>GF_X numeric row id. Original business key is preserved as a data column when its name is not Id.</t>
+    <t>GF_X numeric row id.</t>
   </si>
   <si>
     <t>Note</t>
   </si>
   <si>
-    <t>对应 EnemyConfig.EnemyId</t>
-  </si>
-  <si>
-    <t>阶段编号：1 / 2 / 3</t>
-  </si>
-  <si>
-    <t>进入本阶段的 HP 百分比：1.0=满血，0.6=60%HP</t>
-  </si>
-  <si>
-    <t>本阶段解锁技能 ID，逗号分隔，叠加不替换</t>
-  </si>
-  <si>
-    <t>本阶段伤害倍率，1.0=无变化</t>
-  </si>
-  <si>
-    <t>阶段转换特效 ID</t>
-  </si>
-  <si>
-    <t>阶段 BGM cue ID</t>
-  </si>
-  <si>
-    <t>v2.1 新增：Boss 死亡时必掉的主题配方 ID（仅 PhaseIndex=3 有效，其余填空）</t>
+    <t>EnemyConfig boss id.</t>
+  </si>
+  <si>
+    <t>Phase number 1..3.</t>
+  </si>
+  <si>
+    <t>First-crossing HP ratio threshold.</t>
+  </si>
+  <si>
+    <t>Comma-separated EnemyAbilityConfig ids enabled in this phase.</t>
+  </si>
+  <si>
+    <t>Legacy participant-skill bridge for the old boss service.</t>
+  </si>
+  <si>
+    <t>Phase damage multiplier.</t>
+  </si>
+  <si>
+    <t>Phase VFX cue.</t>
+  </si>
+  <si>
+    <t>Existing audio cue id.</t>
+  </si>
+  <si>
+    <t>Theme recipe emitted by phase three death.</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>enemy_ai_ruins_boss_01</t>
-  </si>
-  <si>
-    <t>1.0</t>
+    <t>boss_ai_core_zero</t>
+  </si>
+  <si>
+    <t>ability_area_emp,ability_beam_core</t>
   </si>
   <si>
     <t>skill_stomp,skill_beam</t>
   </si>
   <si>
-    <t>vfx_boss_enter</t>
+    <t>vfx_boss_ai_phase1</t>
   </si>
   <si>
     <t>bgm_boss_phase1</t>
@@ -113,13 +121,16 @@
     <t>0.6</t>
   </si>
   <si>
+    <t>ability_summon_servo,ability_hazard_overload</t>
+  </si>
+  <si>
     <t>skill_summon</t>
   </si>
   <si>
     <t>1.18</t>
   </si>
   <si>
-    <t>vfx_boss_phase2</t>
+    <t>vfx_boss_ai_phase2</t>
   </si>
   <si>
     <t>bgm_boss_phase2</t>
@@ -131,19 +142,103 @@
     <t>0.3</t>
   </si>
   <si>
+    <t>ability_phase_transition,ability_beam_core,ability_hazard_overload</t>
+  </si>
+  <si>
     <t>skill_enrage_aoe</t>
   </si>
   <si>
-    <t>1.35</t>
-  </si>
-  <si>
-    <t>vfx_boss_phase3</t>
+    <t>1.38</t>
+  </si>
+  <si>
+    <t>vfx_boss_ai_phase3</t>
   </si>
   <si>
     <t>bgm_boss_phase3</t>
   </si>
   <si>
     <t>recipe_ai_ruins_boss</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>boss_alien_hive_mother</t>
+  </si>
+  <si>
+    <t>ability_cone_alien,ability_hazard_acid</t>
+  </si>
+  <si>
+    <t>skill_stomp</t>
+  </si>
+  <si>
+    <t>vfx_boss_alien_phase1</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>ability_summon_crawler,ability_hazard_acid</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>vfx_boss_alien_phase2</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>ability_phase_transition,ability_cone_alien,ability_summon_crawler</t>
+  </si>
+  <si>
+    <t>1.4</t>
+  </si>
+  <si>
+    <t>vfx_boss_alien_phase3</t>
+  </si>
+  <si>
+    <t>recipe_alien_hive_boss</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>boss_virus_terminus</t>
+  </si>
+  <si>
+    <t>ability_charge_boss,ability_hazard_virus</t>
+  </si>
+  <si>
+    <t>vfx_boss_virus_phase1</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>ability_summon_spore,ability_regenerate_spore</t>
+  </si>
+  <si>
+    <t>1.22</t>
+  </si>
+  <si>
+    <t>vfx_boss_virus_phase2</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>ability_phase_transition,ability_charge_boss,ability_death_burst_spore</t>
+  </si>
+  <si>
+    <t>1.42</t>
+  </si>
+  <si>
+    <t>vfx_boss_virus_phase3</t>
+  </si>
+  <si>
+    <t>recipe_virus_swamp_boss</t>
   </si>
 </sst>
 </file>
@@ -154,7 +249,10 @@
   <fonts count="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -175,22 +273,389 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
@@ -234,40 +699,46 @@
       <c r="K2" s="0" t="s">
         <v>11</v>
       </c>
+      <c r="L2" s="0" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="0" t="s">
-        <v>12</v>
-      </c>
       <c r="F3" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="0" t="s">
         <v>14</v>
-      </c>
-      <c r="G3" s="0" t="s">
-        <v>13</v>
       </c>
       <c r="H3" s="0" t="s">
         <v>14</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J3" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="L3" s="0" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -275,34 +746,37 @@
         <v>0</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J4" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K4" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="L4" s="0" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -310,33 +784,36 @@
         <v>3</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5" s="0" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F5" s="0" t="s">
         <v>27</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H5" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="0" t="s">
-        <v>29</v>
-      </c>
       <c r="J5" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K5" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="0" t="s">
         <v>3</v>
       </c>
     </row>
@@ -345,33 +822,36 @@
         <v>3</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C6" s="0" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J6" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K6" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="L6" s="0" t="s">
         <v>3</v>
       </c>
     </row>
@@ -380,37 +860,269 @@
         <v>3</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G7" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="K7" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="L7" s="0" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="I8" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="K8" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="H9" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="J9" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="K9" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="0" t="s">
+      <c r="L9" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="I7" s="0" t="s">
+      <c r="F10" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="J7" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="K7" s="0" t="s">
+      <c r="G10" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" s="0" t="s">
         <v>43</v>
       </c>
+      <c r="I10" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="J10" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="K10" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="L10" s="0" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="H11" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="I11" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="K11" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="L11" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="H12" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="I12" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="J12" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="K12" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="L12" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="H13" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="I13" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="J13" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="K13" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="L13" s="0" t="s">
+        <v>74</v>
+      </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>